--- a/Excel+LAB+4+Dataset_Dmart.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DMart_sales_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D14A585-B8F6-452D-9F49-4874DD4048D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145724B3-E89F-4D0E-A0F2-3C6E7E315004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1787,7 +1787,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF006100"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2153,28 +2171,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}" name="DMart_Sales_Table" displayName="DMart_Sales_Table" ref="A1:Q499" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17">
-  <autoFilter ref="A1:Q499" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}" name="DMart_Sales_Table" displayName="DMart_Sales_Table" ref="A1:Q499" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
+  <autoFilter ref="A1:Q499" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}">
+    <filterColumn colId="4">
+      <colorFilter dxfId="0" cellColor="0"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{F5E12D93-0106-45F5-85DC-E8B1F8D53101}" name="Column1" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{14CC4549-ABDD-4DF7-B22B-1171582C1EB5}" name="Update_region" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{73F60E5C-6410-4EBC-BF8F-48147ED2B06D}" name="Region" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{5601AE86-639E-4ECB-8F37-EDEFA0C621B2}" name="Category" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{18189A26-37C2-4876-9484-BEBC1AF8C1D8}" name="sales" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{14F99767-DBCE-4AC8-8259-97A59E1EB21C}" name="discount" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{DBE0F0B5-C83B-4F9F-BBC9-FA335DF75EE9}" name="quantity" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{AA8C96D2-0B1B-452D-8572-5BCBBE0495E8}" name="order_date" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{69FB3965-E9D4-4A59-9D12-1AE18D3E43CA}" name="delivery_date" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{994325DC-9A01-43E7-96B5-20D7ED627202}" name="customer_type" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{C41D40E6-7D82-473E-BE13-9FD9311B0CCB}" name="customer_type2" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{F1EE67FC-2DD9-4BA1-8241-EA212EF984BD}" name="payment_mode" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{63A44F88-01FF-4BB3-ABA5-BEE30D42E51C}" name="profit" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{C6E2D886-D72C-4D61-B19E-82E2E3535F60}" name="Update_city" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{C9894995-1ABD-4C38-9573-DD7C755DF436}" name="city" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{904796C4-E3D6-42DE-801D-677911EF34FE}" name="UPDATE CITY" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{F5E12D93-0106-45F5-85DC-E8B1F8D53101}" name="Column1" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{14CC4549-ABDD-4DF7-B22B-1171582C1EB5}" name="Update_region" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{73F60E5C-6410-4EBC-BF8F-48147ED2B06D}" name="Region" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{5601AE86-639E-4ECB-8F37-EDEFA0C621B2}" name="Category" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{18189A26-37C2-4876-9484-BEBC1AF8C1D8}" name="sales" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{14F99767-DBCE-4AC8-8259-97A59E1EB21C}" name="discount" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{DBE0F0B5-C83B-4F9F-BBC9-FA335DF75EE9}" name="quantity" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{AA8C96D2-0B1B-452D-8572-5BCBBE0495E8}" name="order_date" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{69FB3965-E9D4-4A59-9D12-1AE18D3E43CA}" name="delivery_date" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{994325DC-9A01-43E7-96B5-20D7ED627202}" name="customer_type" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{C41D40E6-7D82-473E-BE13-9FD9311B0CCB}" name="customer_type2" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{F1EE67FC-2DD9-4BA1-8241-EA212EF984BD}" name="payment_mode" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{63A44F88-01FF-4BB3-ABA5-BEE30D42E51C}" name="profit" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{C6E2D886-D72C-4D61-B19E-82E2E3535F60}" name="Update_city" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{C9894995-1ABD-4C38-9573-DD7C755DF436}" name="city" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{904796C4-E3D6-42DE-801D-677911EF34FE}" name="UPDATE CITY" dataDxfId="3">
       <calculatedColumnFormula>PROPER(DMart_Sales_Table[[#This Row],[city]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{5E9ED336-14EA-4113-BF17-D1523D824F5A}" name="update region" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{5E9ED336-14EA-4113-BF17-D1523D824F5A}" name="update region" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2465,7 +2487,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -2530,7 +2552,7 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -2595,7 +2617,7 @@
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -2660,7 +2682,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -2725,7 +2747,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -2790,7 +2812,7 @@
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -2855,7 +2877,7 @@
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -2920,7 +2942,7 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>39</v>
       </c>
@@ -3050,7 +3072,7 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -3115,7 +3137,7 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -3180,7 +3202,7 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
@@ -3245,7 +3267,7 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>47</v>
       </c>
@@ -3310,7 +3332,7 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,7 +3397,7 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -3440,7 +3462,7 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -3505,7 +3527,7 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -3570,7 +3592,7 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>54</v>
       </c>
@@ -3635,7 +3657,7 @@
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>55</v>
       </c>
@@ -3765,7 +3787,7 @@
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -3830,7 +3852,7 @@
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
@@ -3895,7 +3917,7 @@
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
@@ -3960,7 +3982,7 @@
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
@@ -4025,7 +4047,7 @@
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -4090,7 +4112,7 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>65</v>
       </c>
@@ -4155,7 +4177,7 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>67</v>
       </c>
@@ -4220,7 +4242,7 @@
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>68</v>
       </c>
@@ -4285,7 +4307,7 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>70</v>
       </c>
@@ -4350,7 +4372,7 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>71</v>
       </c>
@@ -4415,7 +4437,7 @@
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>72</v>
       </c>
@@ -4480,7 +4502,7 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
     </row>
-    <row r="33" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>73</v>
       </c>
@@ -4545,7 +4567,7 @@
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
     </row>
-    <row r="34" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>74</v>
       </c>
@@ -4610,7 +4632,7 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
     </row>
-    <row r="35" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>75</v>
       </c>
@@ -4675,7 +4697,7 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
     </row>
-    <row r="36" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>76</v>
       </c>
@@ -4740,7 +4762,7 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
     </row>
-    <row r="37" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>77</v>
       </c>
@@ -4805,7 +4827,7 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
     </row>
-    <row r="38" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>78</v>
       </c>
@@ -4870,7 +4892,7 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
     </row>
-    <row r="39" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>79</v>
       </c>
@@ -4935,7 +4957,7 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
     </row>
-    <row r="40" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>81</v>
       </c>
@@ -5000,7 +5022,7 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
     </row>
-    <row r="41" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -5065,7 +5087,7 @@
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
     </row>
-    <row r="42" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -5130,7 +5152,7 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
     </row>
-    <row r="43" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>84</v>
       </c>
@@ -5195,7 +5217,7 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
     </row>
-    <row r="44" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>85</v>
       </c>
@@ -5260,7 +5282,7 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
     </row>
-    <row r="45" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>86</v>
       </c>
@@ -5325,7 +5347,7 @@
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
     </row>
-    <row r="46" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>87</v>
       </c>
@@ -5390,7 +5412,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>88</v>
       </c>
@@ -5455,7 +5477,7 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
     </row>
-    <row r="48" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>89</v>
       </c>
@@ -5520,7 +5542,7 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
     </row>
-    <row r="49" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>90</v>
       </c>
@@ -5585,7 +5607,7 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
     </row>
-    <row r="50" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>91</v>
       </c>
@@ -5650,7 +5672,7 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
     </row>
-    <row r="51" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>92</v>
       </c>
@@ -5715,7 +5737,7 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
     </row>
-    <row r="52" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>93</v>
       </c>
@@ -5780,7 +5802,7 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
     </row>
-    <row r="53" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>94</v>
       </c>
@@ -5845,7 +5867,7 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
     </row>
-    <row r="54" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>95</v>
       </c>
@@ -5910,7 +5932,7 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
     </row>
-    <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>97</v>
       </c>
@@ -5975,7 +5997,7 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>98</v>
       </c>
@@ -6040,7 +6062,7 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>99</v>
       </c>
@@ -6105,7 +6127,7 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>100</v>
       </c>
@@ -6170,7 +6192,7 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>102</v>
       </c>
@@ -6235,7 +6257,7 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>103</v>
       </c>
@@ -6300,7 +6322,7 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>104</v>
       </c>
@@ -6365,7 +6387,7 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>105</v>
       </c>
@@ -6430,7 +6452,7 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>106</v>
       </c>
@@ -6495,7 +6517,7 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>107</v>
       </c>
@@ -6560,7 +6582,7 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>108</v>
       </c>
@@ -6625,7 +6647,7 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>109</v>
       </c>
@@ -6690,7 +6712,7 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>110</v>
       </c>
@@ -6755,7 +6777,7 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
     </row>
-    <row r="68" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>111</v>
       </c>
@@ -6820,7 +6842,7 @@
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>112</v>
       </c>
@@ -6885,7 +6907,7 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>113</v>
       </c>
@@ -6950,7 +6972,7 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
     </row>
-    <row r="71" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>114</v>
       </c>
@@ -7015,7 +7037,7 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
     </row>
-    <row r="72" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>115</v>
       </c>
@@ -7080,7 +7102,7 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
     </row>
-    <row r="73" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>116</v>
       </c>
@@ -7145,7 +7167,7 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
     </row>
-    <row r="74" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>117</v>
       </c>
@@ -7210,7 +7232,7 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
     </row>
-    <row r="75" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>118</v>
       </c>
@@ -7275,7 +7297,7 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
     </row>
-    <row r="76" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>119</v>
       </c>
@@ -7340,7 +7362,7 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
     </row>
-    <row r="77" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>120</v>
       </c>
@@ -7470,7 +7492,7 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
     </row>
-    <row r="79" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>122</v>
       </c>
@@ -7535,7 +7557,7 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
     </row>
-    <row r="80" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>123</v>
       </c>
@@ -7600,7 +7622,7 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
     </row>
-    <row r="81" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>124</v>
       </c>
@@ -7665,7 +7687,7 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
     </row>
-    <row r="82" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>125</v>
       </c>
@@ -7730,7 +7752,7 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
     </row>
-    <row r="83" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>126</v>
       </c>
@@ -7795,7 +7817,7 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
     </row>
-    <row r="84" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>127</v>
       </c>
@@ -7860,7 +7882,7 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
     </row>
-    <row r="85" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>128</v>
       </c>
@@ -7925,7 +7947,7 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
     </row>
-    <row r="86" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>129</v>
       </c>
@@ -7990,7 +8012,7 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
     </row>
-    <row r="87" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>130</v>
       </c>
@@ -8055,7 +8077,7 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
     </row>
-    <row r="88" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>131</v>
       </c>
@@ -8120,7 +8142,7 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
     </row>
-    <row r="89" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>132</v>
       </c>
@@ -8185,7 +8207,7 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
     </row>
-    <row r="90" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>133</v>
       </c>
@@ -8250,7 +8272,7 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
     </row>
-    <row r="91" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>134</v>
       </c>
@@ -8315,7 +8337,7 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
     </row>
-    <row r="92" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>135</v>
       </c>
@@ -8380,7 +8402,7 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
     </row>
-    <row r="93" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>136</v>
       </c>
@@ -8445,7 +8467,7 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
     </row>
-    <row r="94" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>137</v>
       </c>
@@ -8510,7 +8532,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>138</v>
       </c>
@@ -8575,7 +8597,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>139</v>
       </c>
@@ -8640,7 +8662,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>140</v>
       </c>
@@ -8705,7 +8727,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>141</v>
       </c>
@@ -8770,7 +8792,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>142</v>
       </c>
@@ -8835,7 +8857,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>143</v>
       </c>
@@ -8900,7 +8922,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>144</v>
       </c>
@@ -8965,7 +8987,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>145</v>
       </c>
@@ -9030,7 +9052,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>146</v>
       </c>
@@ -9095,7 +9117,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>147</v>
       </c>
@@ -9160,7 +9182,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>148</v>
       </c>
@@ -9290,7 +9312,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>150</v>
       </c>
@@ -9355,7 +9377,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>151</v>
       </c>
@@ -9485,7 +9507,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>153</v>
       </c>
@@ -9550,7 +9572,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>154</v>
       </c>
@@ -9615,7 +9637,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>155</v>
       </c>
@@ -9680,7 +9702,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>156</v>
       </c>
@@ -9745,7 +9767,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>157</v>
       </c>
@@ -9810,7 +9832,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>158</v>
       </c>
@@ -9875,7 +9897,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>159</v>
       </c>
@@ -9940,7 +9962,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>160</v>
       </c>
@@ -10005,7 +10027,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>161</v>
       </c>
@@ -10070,7 +10092,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>162</v>
       </c>
@@ -10135,7 +10157,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>163</v>
       </c>
@@ -10200,7 +10222,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>164</v>
       </c>
@@ -10265,7 +10287,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>165</v>
       </c>
@@ -10330,7 +10352,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>166</v>
       </c>
@@ -10395,7 +10417,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>167</v>
       </c>
@@ -10460,7 +10482,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>168</v>
       </c>
@@ -10525,7 +10547,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>169</v>
       </c>
@@ -10590,7 +10612,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>170</v>
       </c>
@@ -10655,7 +10677,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>171</v>
       </c>
@@ -10720,7 +10742,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>172</v>
       </c>
@@ -10785,7 +10807,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>173</v>
       </c>
@@ -10850,7 +10872,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>174</v>
       </c>
@@ -10915,7 +10937,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>175</v>
       </c>
@@ -10980,7 +11002,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>176</v>
       </c>
@@ -11045,7 +11067,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>177</v>
       </c>
@@ -11110,7 +11132,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>178</v>
       </c>
@@ -11175,7 +11197,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>179</v>
       </c>
@@ -11240,7 +11262,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>180</v>
       </c>
@@ -11305,7 +11327,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>181</v>
       </c>
@@ -11370,7 +11392,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>182</v>
       </c>
@@ -11435,7 +11457,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>183</v>
       </c>
@@ -11500,7 +11522,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>184</v>
       </c>
@@ -11565,7 +11587,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>185</v>
       </c>
@@ -11630,7 +11652,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>186</v>
       </c>
@@ -11695,7 +11717,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>187</v>
       </c>
@@ -11760,7 +11782,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>188</v>
       </c>
@@ -11825,7 +11847,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>189</v>
       </c>
@@ -11890,7 +11912,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>190</v>
       </c>
@@ -11955,7 +11977,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>191</v>
       </c>
@@ -12020,7 +12042,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>192</v>
       </c>
@@ -12085,7 +12107,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>193</v>
       </c>
@@ -12150,7 +12172,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>194</v>
       </c>
@@ -12215,7 +12237,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>195</v>
       </c>
@@ -12280,7 +12302,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>196</v>
       </c>
@@ -12345,7 +12367,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>197</v>
       </c>
@@ -12410,7 +12432,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>198</v>
       </c>
@@ -12475,7 +12497,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>199</v>
       </c>
@@ -12540,7 +12562,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>200</v>
       </c>
@@ -12605,7 +12627,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>201</v>
       </c>
@@ -12670,7 +12692,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>202</v>
       </c>
@@ -12735,7 +12757,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>203</v>
       </c>
@@ -12800,7 +12822,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>204</v>
       </c>
@@ -12865,7 +12887,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>205</v>
       </c>
@@ -12930,7 +12952,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>206</v>
       </c>
@@ -12995,7 +13017,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>207</v>
       </c>
@@ -13060,7 +13082,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>208</v>
       </c>
@@ -13125,7 +13147,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>209</v>
       </c>
@@ -13255,7 +13277,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>211</v>
       </c>
@@ -13320,7 +13342,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>212</v>
       </c>
@@ -13385,7 +13407,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>213</v>
       </c>
@@ -13450,7 +13472,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>214</v>
       </c>
@@ -13515,7 +13537,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>215</v>
       </c>
@@ -13580,7 +13602,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>216</v>
       </c>
@@ -13645,7 +13667,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>217</v>
       </c>
@@ -13710,7 +13732,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>218</v>
       </c>
@@ -13775,7 +13797,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>219</v>
       </c>
@@ -13840,7 +13862,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>220</v>
       </c>
@@ -13905,7 +13927,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>221</v>
       </c>
@@ -13970,7 +13992,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>222</v>
       </c>
@@ -14035,7 +14057,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>223</v>
       </c>
@@ -14100,7 +14122,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>224</v>
       </c>
@@ -14165,7 +14187,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>225</v>
       </c>
@@ -14230,7 +14252,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>226</v>
       </c>
@@ -14295,7 +14317,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>227</v>
       </c>
@@ -14360,7 +14382,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>228</v>
       </c>
@@ -14425,7 +14447,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>229</v>
       </c>
@@ -14490,7 +14512,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>230</v>
       </c>
@@ -14555,7 +14577,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>231</v>
       </c>
@@ -14620,7 +14642,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>232</v>
       </c>
@@ -14685,7 +14707,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>233</v>
       </c>
@@ -14750,7 +14772,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>234</v>
       </c>
@@ -14815,7 +14837,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>235</v>
       </c>
@@ -14880,7 +14902,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>236</v>
       </c>
@@ -14945,7 +14967,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>237</v>
       </c>
@@ -15010,7 +15032,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>238</v>
       </c>
@@ -15075,7 +15097,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>239</v>
       </c>
@@ -15140,7 +15162,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>240</v>
       </c>
@@ -15205,7 +15227,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>241</v>
       </c>
@@ -15270,7 +15292,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>242</v>
       </c>
@@ -15335,7 +15357,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>243</v>
       </c>
@@ -15400,7 +15422,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>244</v>
       </c>
@@ -15465,7 +15487,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>245</v>
       </c>
@@ -15530,7 +15552,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>246</v>
       </c>
@@ -15595,7 +15617,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>247</v>
       </c>
@@ -15660,7 +15682,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>248</v>
       </c>
@@ -15725,7 +15747,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>249</v>
       </c>
@@ -15790,7 +15812,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>250</v>
       </c>
@@ -15855,7 +15877,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>251</v>
       </c>
@@ -15920,7 +15942,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>252</v>
       </c>
@@ -15985,7 +16007,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>253</v>
       </c>
@@ -16050,7 +16072,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>254</v>
       </c>
@@ -16115,7 +16137,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>255</v>
       </c>
@@ -16180,7 +16202,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>256</v>
       </c>
@@ -16245,7 +16267,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>257</v>
       </c>
@@ -16310,7 +16332,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>258</v>
       </c>
@@ -16375,7 +16397,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>259</v>
       </c>
@@ -16440,7 +16462,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>260</v>
       </c>
@@ -16505,7 +16527,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>261</v>
       </c>
@@ -16570,7 +16592,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>262</v>
       </c>
@@ -16635,7 +16657,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>263</v>
       </c>
@@ -16700,7 +16722,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>264</v>
       </c>
@@ -16765,7 +16787,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>265</v>
       </c>
@@ -16830,7 +16852,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>266</v>
       </c>
@@ -16895,7 +16917,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>267</v>
       </c>
@@ -16960,7 +16982,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>268</v>
       </c>
@@ -17025,7 +17047,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>269</v>
       </c>
@@ -17090,7 +17112,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>270</v>
       </c>
@@ -17155,7 +17177,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>271</v>
       </c>
@@ -17220,7 +17242,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>272</v>
       </c>
@@ -17285,7 +17307,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>273</v>
       </c>
@@ -17350,7 +17372,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>274</v>
       </c>
@@ -17415,7 +17437,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>275</v>
       </c>
@@ -17480,7 +17502,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>276</v>
       </c>
@@ -17545,7 +17567,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>277</v>
       </c>
@@ -17610,7 +17632,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>278</v>
       </c>
@@ -17675,7 +17697,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>279</v>
       </c>
@@ -17740,7 +17762,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>280</v>
       </c>
@@ -17805,7 +17827,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>281</v>
       </c>
@@ -17870,7 +17892,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>282</v>
       </c>
@@ -17935,7 +17957,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>283</v>
       </c>
@@ -18000,7 +18022,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>284</v>
       </c>
@@ -18065,7 +18087,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>285</v>
       </c>
@@ -18130,7 +18152,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>286</v>
       </c>
@@ -18195,7 +18217,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>287</v>
       </c>
@@ -18260,7 +18282,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>288</v>
       </c>
@@ -18325,7 +18347,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>289</v>
       </c>
@@ -18390,7 +18412,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>290</v>
       </c>
@@ -18455,7 +18477,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>291</v>
       </c>
@@ -18520,7 +18542,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>292</v>
       </c>
@@ -18585,7 +18607,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>293</v>
       </c>
@@ -18650,7 +18672,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>294</v>
       </c>
@@ -18715,7 +18737,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>295</v>
       </c>
@@ -18780,7 +18802,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>296</v>
       </c>
@@ -18845,7 +18867,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>297</v>
       </c>
@@ -18910,7 +18932,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>298</v>
       </c>
@@ -18975,7 +18997,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>299</v>
       </c>
@@ -19040,7 +19062,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>300</v>
       </c>
@@ -19105,7 +19127,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>301</v>
       </c>
@@ -19170,7 +19192,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>302</v>
       </c>
@@ -19235,7 +19257,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>303</v>
       </c>
@@ -19300,7 +19322,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>304</v>
       </c>
@@ -19365,7 +19387,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>305</v>
       </c>
@@ -19430,7 +19452,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>306</v>
       </c>
@@ -19495,7 +19517,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>307</v>
       </c>
@@ -19560,7 +19582,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>308</v>
       </c>
@@ -19625,7 +19647,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>309</v>
       </c>
@@ -19690,7 +19712,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>310</v>
       </c>
@@ -19755,7 +19777,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>311</v>
       </c>
@@ -19820,7 +19842,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>312</v>
       </c>
@@ -19950,7 +19972,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>314</v>
       </c>
@@ -20015,7 +20037,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>315</v>
       </c>
@@ -20080,7 +20102,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>316</v>
       </c>
@@ -20145,7 +20167,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>317</v>
       </c>
@@ -20275,7 +20297,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>319</v>
       </c>
@@ -20340,7 +20362,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>320</v>
       </c>
@@ -20405,7 +20427,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>321</v>
       </c>
@@ -20470,7 +20492,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>322</v>
       </c>
@@ -20535,7 +20557,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>323</v>
       </c>
@@ -20600,7 +20622,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>324</v>
       </c>
@@ -20665,7 +20687,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>325</v>
       </c>
@@ -20730,7 +20752,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>326</v>
       </c>
@@ -20795,7 +20817,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>327</v>
       </c>
@@ -20860,7 +20882,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>328</v>
       </c>
@@ -20925,7 +20947,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>329</v>
       </c>
@@ -20990,7 +21012,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>330</v>
       </c>
@@ -21055,7 +21077,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>331</v>
       </c>
@@ -21120,7 +21142,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>332</v>
       </c>
@@ -21185,7 +21207,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>333</v>
       </c>
@@ -21250,7 +21272,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>334</v>
       </c>
@@ -21315,7 +21337,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>335</v>
       </c>
@@ -21380,7 +21402,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>336</v>
       </c>
@@ -21445,7 +21467,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>337</v>
       </c>
@@ -21510,7 +21532,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>338</v>
       </c>
@@ -21575,7 +21597,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>339</v>
       </c>
@@ -21640,7 +21662,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>340</v>
       </c>
@@ -21705,7 +21727,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>341</v>
       </c>
@@ -21770,7 +21792,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>342</v>
       </c>
@@ -21835,7 +21857,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>343</v>
       </c>
@@ -21900,7 +21922,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>344</v>
       </c>
@@ -21965,7 +21987,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>345</v>
       </c>
@@ -22030,7 +22052,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>346</v>
       </c>
@@ -22095,7 +22117,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>347</v>
       </c>
@@ -22160,7 +22182,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>348</v>
       </c>
@@ -22225,7 +22247,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>349</v>
       </c>
@@ -22290,7 +22312,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>350</v>
       </c>
@@ -22355,7 +22377,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>351</v>
       </c>
@@ -22420,7 +22442,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>352</v>
       </c>
@@ -22485,7 +22507,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>353</v>
       </c>
@@ -22550,7 +22572,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>354</v>
       </c>
@@ -22615,7 +22637,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>355</v>
       </c>
@@ -22680,7 +22702,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>356</v>
       </c>
@@ -22745,7 +22767,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>357</v>
       </c>
@@ -22810,7 +22832,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>358</v>
       </c>
@@ -22875,7 +22897,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>359</v>
       </c>
@@ -22940,7 +22962,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>360</v>
       </c>
@@ -23005,7 +23027,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>361</v>
       </c>
@@ -23070,7 +23092,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>362</v>
       </c>
@@ -23135,7 +23157,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>363</v>
       </c>
@@ -23200,7 +23222,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>364</v>
       </c>
@@ -23265,7 +23287,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>365</v>
       </c>
@@ -23330,7 +23352,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>366</v>
       </c>
@@ -23395,7 +23417,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>367</v>
       </c>
@@ -23460,7 +23482,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>368</v>
       </c>
@@ -23525,7 +23547,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>369</v>
       </c>
@@ -23590,7 +23612,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>370</v>
       </c>
@@ -23655,7 +23677,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>371</v>
       </c>
@@ -23720,7 +23742,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>372</v>
       </c>
@@ -23785,7 +23807,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>373</v>
       </c>
@@ -23850,7 +23872,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>374</v>
       </c>
@@ -23915,7 +23937,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>375</v>
       </c>
@@ -23980,7 +24002,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>376</v>
       </c>
@@ -24045,7 +24067,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>377</v>
       </c>
@@ -24110,7 +24132,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>378</v>
       </c>
@@ -24175,7 +24197,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>379</v>
       </c>
@@ -24240,7 +24262,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>380</v>
       </c>
@@ -24305,7 +24327,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>381</v>
       </c>
@@ -24370,7 +24392,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>382</v>
       </c>
@@ -24435,7 +24457,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>383</v>
       </c>
@@ -24500,7 +24522,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>384</v>
       </c>
@@ -24565,7 +24587,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>385</v>
       </c>
@@ -24630,7 +24652,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>386</v>
       </c>
@@ -24695,7 +24717,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>387</v>
       </c>
@@ -24760,7 +24782,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>388</v>
       </c>
@@ -24825,7 +24847,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>389</v>
       </c>
@@ -24890,7 +24912,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>390</v>
       </c>
@@ -24955,7 +24977,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>391</v>
       </c>
@@ -25020,7 +25042,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>392</v>
       </c>
@@ -25085,7 +25107,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>393</v>
       </c>
@@ -25150,7 +25172,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>394</v>
       </c>
@@ -25215,7 +25237,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>395</v>
       </c>
@@ -25280,7 +25302,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>396</v>
       </c>
@@ -25345,7 +25367,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>397</v>
       </c>
@@ -25410,7 +25432,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>398</v>
       </c>
@@ -25475,7 +25497,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>399</v>
       </c>
@@ -25540,7 +25562,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>400</v>
       </c>
@@ -25605,7 +25627,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>401</v>
       </c>
@@ -25670,7 +25692,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>402</v>
       </c>
@@ -25735,7 +25757,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>403</v>
       </c>
@@ -25800,7 +25822,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>404</v>
       </c>
@@ -25865,7 +25887,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>405</v>
       </c>
@@ -25930,7 +25952,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>406</v>
       </c>
@@ -25995,7 +26017,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>407</v>
       </c>
@@ -26060,7 +26082,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>408</v>
       </c>
@@ -26125,7 +26147,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>409</v>
       </c>
@@ -26190,7 +26212,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>410</v>
       </c>
@@ -26255,7 +26277,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>411</v>
       </c>
@@ -26320,7 +26342,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>412</v>
       </c>
@@ -26385,7 +26407,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>413</v>
       </c>
@@ -26450,7 +26472,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>414</v>
       </c>
@@ -26515,7 +26537,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>415</v>
       </c>
@@ -26580,7 +26602,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>416</v>
       </c>
@@ -26645,7 +26667,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>417</v>
       </c>
@@ -26710,7 +26732,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>418</v>
       </c>
@@ -26775,7 +26797,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>419</v>
       </c>
@@ -26840,7 +26862,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>420</v>
       </c>
@@ -26905,7 +26927,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>421</v>
       </c>
@@ -26970,7 +26992,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>422</v>
       </c>
@@ -27035,7 +27057,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>423</v>
       </c>
@@ -27100,7 +27122,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>424</v>
       </c>
@@ -27165,7 +27187,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>425</v>
       </c>
@@ -27230,7 +27252,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>426</v>
       </c>
@@ -27295,7 +27317,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>427</v>
       </c>
@@ -27360,7 +27382,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>428</v>
       </c>
@@ -27425,7 +27447,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>429</v>
       </c>
@@ -27490,7 +27512,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>430</v>
       </c>
@@ -27555,7 +27577,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>431</v>
       </c>
@@ -27620,7 +27642,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>432</v>
       </c>
@@ -27750,7 +27772,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>434</v>
       </c>
@@ -27815,7 +27837,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>435</v>
       </c>
@@ -27880,7 +27902,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>436</v>
       </c>
@@ -27945,7 +27967,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>437</v>
       </c>
@@ -28010,7 +28032,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>438</v>
       </c>
@@ -28075,7 +28097,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>439</v>
       </c>
@@ -28140,7 +28162,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>440</v>
       </c>
@@ -28205,7 +28227,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>441</v>
       </c>
@@ -28270,7 +28292,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>442</v>
       </c>
@@ -28335,7 +28357,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>443</v>
       </c>
@@ -28400,7 +28422,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>444</v>
       </c>
@@ -28465,7 +28487,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>445</v>
       </c>
@@ -28530,7 +28552,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>446</v>
       </c>
@@ -28595,7 +28617,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>447</v>
       </c>
@@ -28660,7 +28682,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>448</v>
       </c>
@@ -28725,7 +28747,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>449</v>
       </c>
@@ -28790,7 +28812,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>450</v>
       </c>
@@ -28855,7 +28877,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>451</v>
       </c>
@@ -28920,7 +28942,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>452</v>
       </c>
@@ -28985,7 +29007,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>453</v>
       </c>
@@ -29050,7 +29072,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>454</v>
       </c>
@@ -29115,7 +29137,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>455</v>
       </c>
@@ -29180,7 +29202,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>456</v>
       </c>
@@ -29245,7 +29267,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>457</v>
       </c>
@@ -29310,7 +29332,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>458</v>
       </c>
@@ -29375,7 +29397,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>459</v>
       </c>
@@ -29440,7 +29462,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>460</v>
       </c>
@@ -29505,7 +29527,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>461</v>
       </c>
@@ -29570,7 +29592,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>462</v>
       </c>
@@ -29635,7 +29657,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>463</v>
       </c>
@@ -29700,7 +29722,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>464</v>
       </c>
@@ -29765,7 +29787,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>465</v>
       </c>
@@ -29830,7 +29852,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>466</v>
       </c>
@@ -29895,7 +29917,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>467</v>
       </c>
@@ -29960,7 +29982,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>468</v>
       </c>
@@ -30025,7 +30047,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>469</v>
       </c>
@@ -30090,7 +30112,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>470</v>
       </c>
@@ -30155,7 +30177,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>471</v>
       </c>
@@ -30220,7 +30242,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>472</v>
       </c>
@@ -30285,7 +30307,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>473</v>
       </c>
@@ -30350,7 +30372,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>474</v>
       </c>
@@ -30415,7 +30437,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>475</v>
       </c>
@@ -30480,7 +30502,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>476</v>
       </c>
@@ -30545,7 +30567,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>477</v>
       </c>
@@ -30610,7 +30632,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>478</v>
       </c>
@@ -30675,7 +30697,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>479</v>
       </c>
@@ -30740,7 +30762,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>480</v>
       </c>
@@ -30805,7 +30827,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>481</v>
       </c>
@@ -30870,7 +30892,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>482</v>
       </c>
@@ -30935,7 +30957,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>483</v>
       </c>
@@ -31000,7 +31022,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>484</v>
       </c>
@@ -31065,7 +31087,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>485</v>
       </c>
@@ -31130,7 +31152,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>486</v>
       </c>
@@ -31195,7 +31217,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>487</v>
       </c>
@@ -31260,7 +31282,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>488</v>
       </c>
@@ -31325,7 +31347,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>489</v>
       </c>
@@ -31390,7 +31412,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>490</v>
       </c>
@@ -31455,7 +31477,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>491</v>
       </c>
@@ -31520,7 +31542,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>492</v>
       </c>
@@ -31585,7 +31607,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>493</v>
       </c>
@@ -31650,7 +31672,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>494</v>
       </c>
@@ -31715,7 +31737,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>495</v>
       </c>
@@ -31780,7 +31802,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>496</v>
       </c>
@@ -31845,7 +31867,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>497</v>
       </c>
@@ -31910,7 +31932,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>498</v>
       </c>
@@ -31975,7 +31997,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>499</v>
       </c>
@@ -32040,7 +32062,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>500</v>
       </c>
@@ -32105,7 +32127,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>501</v>
       </c>
@@ -32170,7 +32192,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>502</v>
       </c>
@@ -32235,7 +32257,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>503</v>
       </c>
@@ -32300,7 +32322,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>504</v>
       </c>
@@ -32365,7 +32387,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>505</v>
       </c>
@@ -32430,7 +32452,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>506</v>
       </c>
@@ -32495,7 +32517,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>507</v>
       </c>
@@ -32560,7 +32582,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>508</v>
       </c>
@@ -32625,7 +32647,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>509</v>
       </c>
@@ -32690,7 +32712,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>510</v>
       </c>
@@ -32755,7 +32777,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>511</v>
       </c>
@@ -32820,7 +32842,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>512</v>
       </c>
@@ -32885,7 +32907,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>513</v>
       </c>
@@ -32950,7 +32972,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>514</v>
       </c>
@@ -33015,7 +33037,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>515</v>
       </c>
@@ -33080,7 +33102,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>516</v>
       </c>
@@ -33145,7 +33167,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>517</v>
       </c>
@@ -33210,7 +33232,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>518</v>
       </c>
@@ -33275,7 +33297,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>519</v>
       </c>
@@ -33340,7 +33362,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>520</v>
       </c>
@@ -33405,7 +33427,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>521</v>
       </c>
@@ -33470,7 +33492,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>522</v>
       </c>
@@ -33535,7 +33557,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>523</v>
       </c>
@@ -33600,7 +33622,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>524</v>
       </c>
@@ -33665,7 +33687,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>525</v>
       </c>
@@ -33730,7 +33752,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>526</v>
       </c>
@@ -33795,7 +33817,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>527</v>
       </c>
@@ -33860,7 +33882,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>528</v>
       </c>
@@ -33925,7 +33947,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>529</v>
       </c>
@@ -33990,7 +34012,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>530</v>
       </c>
@@ -34055,7 +34077,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>531</v>
       </c>
@@ -34120,7 +34142,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>532</v>
       </c>
@@ -34250,7 +34272,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>534</v>
       </c>
@@ -34315,7 +34337,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>535</v>
       </c>
@@ -34380,7 +34402,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>536</v>
       </c>
@@ -34445,7 +34467,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>537</v>
       </c>
@@ -34510,7 +34532,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>538</v>
       </c>
@@ -34575,7 +34597,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>539</v>
       </c>
@@ -34640,7 +34662,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>540</v>
       </c>
@@ -34705,7 +34727,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>541</v>
       </c>
@@ -34770,7 +34792,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:28" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>542</v>
       </c>
@@ -48865,6 +48887,19 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color theme="9" tint="-0.249977111117893"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
